--- a/cms/Corte_Forms_2026-09-17_115657.xlsx
+++ b/cms/Corte_Forms_2026-09-17_115657.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ecesar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84063EC5-2DFC-4324-9C38-C709B515FAB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D64A512-63A5-4C48-A587-7F3D3F07C9CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15198,7 +15198,7 @@
         <v>251</v>
       </c>
       <c r="F213" s="10">
-        <v>38599</v>
+        <v>38590</v>
       </c>
       <c r="G213" s="10" t="s">
         <v>22</v>
@@ -18086,7 +18086,7 @@
         <v>1040</v>
       </c>
       <c r="F274" s="10">
-        <v>94565</v>
+        <v>38764</v>
       </c>
       <c r="G274" s="10" t="s">
         <v>16</v>
